--- a/lucas/import_data/utility/landscape/excel/land_use_order.xlsx
+++ b/lucas/import_data/utility/landscape/excel/land_use_order.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -31,6 +31,9 @@
     <t xml:space="preserve">display_name</t>
   </si>
   <si>
+    <t xml:space="preserve">tag</t>
+  </si>
+  <si>
     <t xml:space="preserve">abstract</t>
   </si>
   <si>
@@ -43,6 +46,9 @@
     <t xml:space="preserve">Primary production</t>
   </si>
   <si>
+    <t xml:space="preserve">nature</t>
+  </si>
+  <si>
     <t xml:space="preserve">Extraction or management of natural earth-based resources</t>
   </si>
   <si>
@@ -55,6 +61,9 @@
     <t xml:space="preserve">Industrial production</t>
   </si>
   <si>
+    <t xml:space="preserve">indutry</t>
+  </si>
+  <si>
     <t xml:space="preserve">Industrial production and manufacturing</t>
   </si>
   <si>
@@ -65,6 +74,9 @@
   </si>
   <si>
     <t xml:space="preserve">Infrastructure services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">infrastructure</t>
   </si>
   <si>
     <t xml:space="preserve">Services and built environment</t>
@@ -94,6 +106,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -153,8 +166,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -178,37 +195,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -281,82 +298,98 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="43.48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="43.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.94"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>11</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>15</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>19</v>
+      <c r="A5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
